--- a/plot/storage/output/ongoing/ongoing_total_q.xlsx
+++ b/plot/storage/output/ongoing/ongoing_total_q.xlsx
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9406666.666666666</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>226574838.6388889</v>
+        <v>191574838.6388889</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>9130000</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>191829941.75</v>
+        <v>152941052.8611111</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>446666.6666666667</v>
+        <v>9023333.333333332</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>202253333.3333333</v>
+        <v>155586666.6666667</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>670000</v>
+        <v>8140000</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>278642222.2222222</v>
+        <v>225308888.8888889</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>26185597.01666667</v>
+        <v>33074212.85</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>330586666.6666666</v>
+        <v>305586666.6666667</v>
       </c>
       <c r="P6" t="n">
         <v>27500</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>43187958.21111111</v>
+        <v>56207746.26666667</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -810,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>330586666.6666666</v>
+        <v>305586666.6666667</v>
       </c>
       <c r="P7" t="n">
         <v>138287.5</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>59770107.41578947</v>
+        <v>78255560.7988304</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>345387500</v>
+        <v>320387500</v>
       </c>
       <c r="P8" t="n">
         <v>174254.1666666667</v>
@@ -901,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>74975172.24035087</v>
+        <v>95281958.56491227</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>471211622.8070176</v>
+        <v>427461622.8070176</v>
       </c>
       <c r="P9" t="n">
         <v>3041337.5</v>
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>76010100.57368422</v>
+        <v>97240029.12046784</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>616869517.5438597</v>
+        <v>535619517.5438596</v>
       </c>
       <c r="P10" t="n">
         <v>4480712.5</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>77450450.57368422</v>
+        <v>93395790.23157895</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1010,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>588279239.7660818</v>
+        <v>507029239.7660819</v>
       </c>
       <c r="P11" t="n">
         <v>20100136.11111111</v>
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>77471065.57368422</v>
+        <v>94004738.56491227</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>934499833.6688597</v>
+        <v>853249833.6688596</v>
       </c>
       <c r="P12" t="n">
         <v>30124594.44444445</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>161794159.4625731</v>
+        <v>173209499.1204678</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>978349093.4902883</v>
+        <v>900432426.8236215</v>
       </c>
       <c r="P13" t="n">
         <v>31312658.33333333</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>173008364.6380117</v>
+        <v>178190924.0210526</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1584839110.322248</v>
+        <v>1513589110.322248</v>
       </c>
       <c r="P14" t="n">
         <v>31934121.05555555</v>
@@ -1201,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>180069362.6</v>
+        <v>181038428.3222222</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1609720574.890961</v>
+        <v>1542359463.77985</v>
       </c>
       <c r="P15" t="n">
         <v>33940485.27777778</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>191175440.4333333</v>
+        <v>191913950.6</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1612673415.324306</v>
+        <v>1553090081.990973</v>
       </c>
       <c r="P16" t="n">
         <v>35505104.5</v>
@@ -1301,7 +1301,7 @@
         <v>322222.2222222222</v>
       </c>
       <c r="L17" t="n">
-        <v>196015334.0444444</v>
+        <v>193579310.8777778</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1310,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1504832959.550973</v>
+        <v>1442749626.21764</v>
       </c>
       <c r="P17" t="n">
         <v>35542867</v>
@@ -1351,7 +1351,7 @@
         <v>12517345.66666667</v>
       </c>
       <c r="L18" t="n">
-        <v>311456333.2992424</v>
+        <v>306437125.2083333</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1271731413.083672</v>
+        <v>1204648079.750338</v>
       </c>
       <c r="P18" t="n">
         <v>37357725.33333334</v>
@@ -1401,7 +1401,7 @@
         <v>10800000</v>
       </c>
       <c r="L19" t="n">
-        <v>374612360.854798</v>
+        <v>366111057.2083333</v>
       </c>
       <c r="M19" t="n">
         <v>1511111.111111111</v>
@@ -1410,7 +1410,7 @@
         <v>9166666.666666666</v>
       </c>
       <c r="O19" t="n">
-        <v>1287604428.956688</v>
+        <v>1220521095.623354</v>
       </c>
       <c r="P19" t="n">
         <v>38163604.5</v>
@@ -1451,7 +1451,7 @@
         <v>16716666.66666667</v>
       </c>
       <c r="L20" t="n">
-        <v>311392830.8230519</v>
+        <v>260726496.6210318</v>
       </c>
       <c r="M20" t="n">
         <v>2266666.666666667</v>
@@ -1460,7 +1460,7 @@
         <v>13750000</v>
       </c>
       <c r="O20" t="n">
-        <v>1367815790.148607</v>
+        <v>1288510234.593051</v>
       </c>
       <c r="P20" t="n">
         <v>52902692.94444445</v>
@@ -1483,13 +1483,13 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>137399508.9722222</v>
+        <v>14641077.91666666</v>
       </c>
       <c r="G21" t="n">
         <v>61111111.11111111</v>
       </c>
       <c r="H21" t="n">
-        <v>366666666.6666667</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>28333333.33333333</v>
@@ -1501,7 +1501,7 @@
         <v>17504166.66666666</v>
       </c>
       <c r="L21" t="n">
-        <v>308024344.7530664</v>
+        <v>267875831.6175249</v>
       </c>
       <c r="M21" t="n">
         <v>2266666.666666667</v>
@@ -1510,7 +1510,7 @@
         <v>13750000</v>
       </c>
       <c r="O21" t="n">
-        <v>1543885234.593051</v>
+        <v>1477218567.926384</v>
       </c>
       <c r="P21" t="n">
         <v>64155672</v>
@@ -1524,7 +1524,7 @@
         <v>808374351.2661978</v>
       </c>
       <c r="C22" t="n">
-        <v>3636363.636363636</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1533,13 +1533,13 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>384334451.5555555</v>
+        <v>16059158.38888889</v>
       </c>
       <c r="G22" t="n">
         <v>91666666.66666667</v>
       </c>
       <c r="H22" t="n">
-        <v>1100000000</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>40555555.55555555</v>
@@ -1551,7 +1551,7 @@
         <v>17897916.66666666</v>
       </c>
       <c r="L22" t="n">
-        <v>319456732.3869048</v>
+        <v>279100366.5522794</v>
       </c>
       <c r="M22" t="n">
         <v>2266666.666666667</v>
@@ -1560,10 +1560,10 @@
         <v>13750000</v>
       </c>
       <c r="O22" t="n">
-        <v>1181974978.182795</v>
+        <v>1152808311.516128</v>
       </c>
       <c r="P22" t="n">
-        <v>70540935.66666666</v>
+        <v>74669140.79487179</v>
       </c>
     </row>
     <row r="23">
@@ -1574,7 +1574,7 @@
         <v>1160876898.13689</v>
       </c>
       <c r="C23" t="n">
-        <v>10909090.90909091</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>794548945.8333333</v>
+        <v>426273652.6666666</v>
       </c>
       <c r="G23" t="n">
         <v>91666666.66666667</v>
       </c>
       <c r="H23" t="n">
-        <v>1100000000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>47448634.5</v>
@@ -1601,7 +1601,7 @@
         <v>17897916.66666666</v>
       </c>
       <c r="L23" t="n">
-        <v>325523459.609127</v>
+        <v>300136404.8856127</v>
       </c>
       <c r="M23" t="n">
         <v>2266666.666666667</v>
@@ -1610,10 +1610,10 @@
         <v>13750000</v>
       </c>
       <c r="O23" t="n">
-        <v>799565671.1758018</v>
+        <v>770399004.5091351</v>
       </c>
       <c r="P23" t="n">
-        <v>69526212.05555555</v>
+        <v>73654417.18376069</v>
       </c>
     </row>
     <row r="24">
@@ -1624,7 +1624,7 @@
         <v>1240206827.678319</v>
       </c>
       <c r="C24" t="n">
-        <v>10909090.90909091</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1633,13 +1633,13 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>749175644.5</v>
+        <v>380900351.3333333</v>
       </c>
       <c r="G24" t="n">
         <v>91666666.66666667</v>
       </c>
       <c r="H24" t="n">
-        <v>1100000000</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>47839618.41666666</v>
@@ -1651,7 +1651,7 @@
         <v>17897916.66666666</v>
       </c>
       <c r="L24" t="n">
-        <v>602710911.2619047</v>
+        <v>585599839.4443735</v>
       </c>
       <c r="M24" t="n">
         <v>2266666.666666667</v>
@@ -1660,10 +1660,10 @@
         <v>13750000</v>
       </c>
       <c r="O24" t="n">
-        <v>903890086.4695081</v>
+        <v>874723419.8028414</v>
       </c>
       <c r="P24" t="n">
-        <v>90572176.02614379</v>
+        <v>65759204.68376069</v>
       </c>
     </row>
     <row r="25">
@@ -1674,7 +1674,7 @@
         <v>1167219759.168345</v>
       </c>
       <c r="C25" t="n">
-        <v>10909090.90909091</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1683,13 +1683,13 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>963739136.5634921</v>
+        <v>381178129.1111111</v>
       </c>
       <c r="G25" t="n">
         <v>91666666.66666667</v>
       </c>
       <c r="H25" t="n">
-        <v>1100000000</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>47839618.41666666</v>
@@ -1701,7 +1701,7 @@
         <v>17897916.66666666</v>
       </c>
       <c r="L25" t="n">
-        <v>459158768.3168498</v>
+        <v>467250540.0890621</v>
       </c>
       <c r="M25" t="n">
         <v>2266666.666666667</v>
@@ -1710,10 +1710,10 @@
         <v>13750000</v>
       </c>
       <c r="O25" t="n">
-        <v>873060706.9972858</v>
+        <v>840560706.9972858</v>
       </c>
       <c r="P25" t="n">
-        <v>1103329583.258467</v>
+        <v>1078516611.916084</v>
       </c>
     </row>
     <row r="26">
@@ -1724,7 +1724,7 @@
         <v>1360206062.397019</v>
       </c>
       <c r="C26" t="n">
-        <v>3636363.636363636</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1733,13 +1733,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>957128025.4523809</v>
+        <v>374567018</v>
       </c>
       <c r="G26" t="n">
         <v>91666666.66666667</v>
       </c>
       <c r="H26" t="n">
-        <v>1100000000</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>47839618.41666666</v>
@@ -1751,7 +1751,7 @@
         <v>22714692.98245614</v>
       </c>
       <c r="L26" t="n">
-        <v>434326337.9201369</v>
+        <v>388960278.1367936</v>
       </c>
       <c r="M26" t="n">
         <v>2266666.666666667</v>
@@ -1760,10 +1760,10 @@
         <v>15949274.38888889</v>
       </c>
       <c r="O26" t="n">
-        <v>872745888.2263768</v>
+        <v>833579221.5597101</v>
       </c>
       <c r="P26" t="n">
-        <v>113511635.2635175</v>
+        <v>84390971.61344211</v>
       </c>
     </row>
     <row r="27">
@@ -1774,7 +1774,7 @@
         <v>1494771925.572232</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1783,13 +1783,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>942794692.1190476</v>
+        <v>360233684.6666667</v>
       </c>
       <c r="G27" t="n">
         <v>91666666.66666667</v>
       </c>
       <c r="H27" t="n">
-        <v>1100000000</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>47839618.41666666</v>
@@ -1801,7 +1801,7 @@
         <v>32348245.61403509</v>
       </c>
       <c r="L27" t="n">
-        <v>324261338.7463691</v>
+        <v>285294926.7408036</v>
       </c>
       <c r="M27" t="n">
         <v>2266666.666666667</v>
@@ -1810,10 +1810,10 @@
         <v>53160022.69444444</v>
       </c>
       <c r="O27" t="n">
-        <v>1064973978.453289</v>
+        <v>1025807311.786622</v>
       </c>
       <c r="P27" t="n">
-        <v>202542382.1524064</v>
+        <v>171267872.3484848</v>
       </c>
     </row>
     <row r="28">
@@ -1821,10 +1821,10 @@
         <v>45199</v>
       </c>
       <c r="B28" t="n">
-        <v>1555001942.52095</v>
+        <v>1510557498.076506</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1833,13 +1833,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>945794692.1190476</v>
+        <v>363233684.6666667</v>
       </c>
       <c r="G28" t="n">
         <v>91666666.66666667</v>
       </c>
       <c r="H28" t="n">
-        <v>1100000000</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>47839618.41666666</v>
@@ -1851,7 +1851,7 @@
         <v>33775491.7251462</v>
       </c>
       <c r="L28" t="n">
-        <v>645667924.8019247</v>
+        <v>2606264869.939217</v>
       </c>
       <c r="M28" t="n">
         <v>2266666.666666667</v>
@@ -1860,10 +1860,10 @@
         <v>71215578.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1136419275.783821</v>
+        <v>1096717886.894932</v>
       </c>
       <c r="P28" t="n">
-        <v>269419568.4857397</v>
+        <v>238145058.6818182</v>
       </c>
     </row>
     <row r="29">
@@ -1871,10 +1871,10 @@
         <v>45291</v>
       </c>
       <c r="B29" t="n">
-        <v>1764281212.922997</v>
+        <v>1697614546.25633</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1883,13 +1883,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>871366120.6904762</v>
+        <v>360233684.6666667</v>
       </c>
       <c r="G29" t="n">
         <v>91666666.66666667</v>
       </c>
       <c r="H29" t="n">
-        <v>1100000000</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>47839618.41666666</v>
@@ -1901,7 +1901,7 @@
         <v>34166892.55847953</v>
       </c>
       <c r="L29" t="n">
-        <v>726436090.4093728</v>
+        <v>692929394.2768232</v>
       </c>
       <c r="M29" t="n">
         <v>85830927.77777778</v>
@@ -1910,10 +1910,10 @@
         <v>71215578.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1268516498.006043</v>
+        <v>1209412331.339376</v>
       </c>
       <c r="P29" t="n">
-        <v>269391321.1372549</v>
+        <v>238116811.3333333</v>
       </c>
     </row>
     <row r="30">
@@ -1921,10 +1921,10 @@
         <v>45382</v>
       </c>
       <c r="B30" t="n">
-        <v>2091461257.443465</v>
+        <v>2024794590.776798</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1933,13 +1933,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>727481200.0555556</v>
+        <v>359205906.8888889</v>
       </c>
       <c r="G30" t="n">
         <v>92333333.33333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1202777777.777778</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>103395173.9722222</v>
@@ -1951,7 +1951,7 @@
         <v>35089114.78070175</v>
       </c>
       <c r="L30" t="n">
-        <v>556103868.6798246</v>
+        <v>527063839.2139416</v>
       </c>
       <c r="M30" t="n">
         <v>170946391.6666667</v>
@@ -1960,10 +1960,10 @@
         <v>71215578.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1475318085.307631</v>
+        <v>1372880585.307631</v>
       </c>
       <c r="P30" t="n">
-        <v>276448330.248366</v>
+        <v>245173820.4444444</v>
       </c>
     </row>
     <row r="31">
@@ -1971,10 +1971,10 @@
         <v>45473</v>
       </c>
       <c r="B31" t="n">
-        <v>2241674086.721243</v>
+        <v>2175007420.054576</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         <v>6944444.444444444</v>
       </c>
       <c r="F31" t="n">
-        <v>726708814.7777778</v>
+        <v>358433521.6111111</v>
       </c>
       <c r="G31" t="n">
         <v>92333333.33333334</v>
       </c>
       <c r="H31" t="n">
-        <v>4567619284.333333</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>111172951.75</v>
@@ -2001,19 +2001,19 @@
         <v>25255781.44736842</v>
       </c>
       <c r="L31" t="n">
-        <v>268302944.2750627</v>
+        <v>237832140.8806083</v>
       </c>
       <c r="M31" t="n">
-        <v>367315920.7222222</v>
+        <v>349990836.1111111</v>
       </c>
       <c r="N31" t="n">
         <v>78715578.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1710698202.266695</v>
+        <v>1608260702.266695</v>
       </c>
       <c r="P31" t="n">
-        <v>295005698.4705882</v>
+        <v>263731188.6666667</v>
       </c>
     </row>
     <row r="32">
@@ -2021,10 +2021,10 @@
         <v>45565</v>
       </c>
       <c r="B32" t="n">
-        <v>2156954863.538703</v>
+        <v>2090288196.872037</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -2033,13 +2033,13 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F32" t="n">
-        <v>3910579566.583333</v>
+        <v>8067304273.416666</v>
       </c>
       <c r="G32" t="n">
         <v>92333333.33333334</v>
       </c>
       <c r="H32" t="n">
-        <v>4567619284.333333</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>111172951.75</v>
@@ -2051,19 +2051,19 @@
         <v>19339114.78070175</v>
       </c>
       <c r="L32" t="n">
-        <v>302934780.7472849</v>
+        <v>265768144.0194972</v>
       </c>
       <c r="M32" t="n">
-        <v>640500685.25</v>
+        <v>710346391.6666666</v>
       </c>
       <c r="N32" t="n">
         <v>75111556.94444445</v>
       </c>
       <c r="O32" t="n">
-        <v>1653076320.180527</v>
+        <v>1617861042.402749</v>
       </c>
       <c r="P32" t="n">
-        <v>259735310.0261438</v>
+        <v>228460800.2222222</v>
       </c>
     </row>
     <row r="33">
@@ -2071,10 +2071,10 @@
         <v>45657</v>
       </c>
       <c r="B33" t="n">
-        <v>1870318880.545532</v>
+        <v>1803652213.878865</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -2083,13 +2083,13 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F33" t="n">
-        <v>2793821135.527778</v>
+        <v>3823304273.416667</v>
       </c>
       <c r="G33" t="n">
         <v>31222222.22222222</v>
       </c>
       <c r="H33" t="n">
-        <v>4601627353.916667</v>
+        <v>400674736.25</v>
       </c>
       <c r="I33" t="n">
         <v>102839618.4166667</v>
@@ -2101,19 +2101,19 @@
         <v>3707535.833333333</v>
       </c>
       <c r="L33" t="n">
-        <v>350539632.8174603</v>
+        <v>294609641.3888179</v>
       </c>
       <c r="M33" t="n">
-        <v>640500685.25</v>
+        <v>710346391.6666666</v>
       </c>
       <c r="N33" t="n">
         <v>77070181</v>
       </c>
       <c r="O33" t="n">
-        <v>1518400183.059012</v>
+        <v>1516796016.392345</v>
       </c>
       <c r="P33" t="n">
-        <v>204617580.9705882</v>
+        <v>173343071.1666667</v>
       </c>
     </row>
     <row r="34">
@@ -2121,10 +2121,10 @@
         <v>45747</v>
       </c>
       <c r="B34" t="n">
-        <v>2088985447.640281</v>
+        <v>2155652114.306947</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -2133,13 +2133,13 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F34" t="n">
-        <v>710633970.7222222</v>
+        <v>360633970.7222222</v>
       </c>
       <c r="G34" t="n">
         <v>666666.6666666666</v>
       </c>
       <c r="H34" t="n">
-        <v>3868294020.583333</v>
+        <v>400674736.25</v>
       </c>
       <c r="I34" t="n">
         <v>90617396.19444445</v>
@@ -2151,19 +2151,19 @@
         <v>3707535.833333333</v>
       </c>
       <c r="L34" t="n">
-        <v>275463099.6785714</v>
+        <v>201532680.8995017</v>
       </c>
       <c r="M34" t="n">
-        <v>640500685.25</v>
+        <v>710346391.6666666</v>
       </c>
       <c r="N34" t="n">
         <v>77070181</v>
       </c>
       <c r="O34" t="n">
-        <v>1339359184.841543</v>
+        <v>1337755018.174876</v>
       </c>
       <c r="P34" t="n">
-        <v>207910428.4150327</v>
+        <v>178969251.9444444</v>
       </c>
     </row>
     <row r="35">
@@ -2171,10 +2171,10 @@
         <v>45838</v>
       </c>
       <c r="B35" t="n">
-        <v>2361028395.008701</v>
+        <v>2527695061.675368</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="D35" t="n">
         <v>7916666.666666667</v>
@@ -2183,13 +2183,13 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F35" t="n">
-        <v>358293365.3333333</v>
+        <v>8293365.333333333</v>
       </c>
       <c r="G35" t="n">
         <v>666666.6666666666</v>
       </c>
       <c r="H35" t="n">
-        <v>3868294020.583333</v>
+        <v>400674736.25</v>
       </c>
       <c r="I35" t="n">
         <v>83724317.25</v>
@@ -2201,19 +2201,19 @@
         <v>3707535.833333333</v>
       </c>
       <c r="L35" t="n">
-        <v>267964632.8134921</v>
+        <v>1878587863.905223</v>
       </c>
       <c r="M35" t="n">
-        <v>640500685.25</v>
+        <v>710346391.6666666</v>
       </c>
       <c r="N35" t="n">
         <v>77070181</v>
       </c>
       <c r="O35" t="n">
-        <v>1340518907.063765</v>
+        <v>1377803629.285987</v>
       </c>
       <c r="P35" t="n">
-        <v>324632891.3235294</v>
+        <v>314985832.5</v>
       </c>
     </row>
     <row r="36">
@@ -2221,7 +2221,7 @@
         <v>45930</v>
       </c>
       <c r="B36" t="n">
-        <v>2165033593.964201</v>
+        <v>2331700260.630867</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -2233,13 +2233,13 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F36" t="n">
-        <v>356666666.6666667</v>
+        <v>6666666.666666666</v>
       </c>
       <c r="G36" t="n">
         <v>666666.6666666666</v>
       </c>
       <c r="H36" t="n">
-        <v>3868294020.583333</v>
+        <v>400674736.25</v>
       </c>
       <c r="I36" t="n">
         <v>83333333.33333333</v>
@@ -2251,16 +2251,16 @@
         <v>3707535.833333333</v>
       </c>
       <c r="L36" t="n">
-        <v>245603072.1666667</v>
+        <v>164800269.6666667</v>
       </c>
       <c r="M36" t="n">
-        <v>640500685.25</v>
+        <v>710346391.6666666</v>
       </c>
       <c r="N36" t="n">
         <v>77070181</v>
       </c>
       <c r="O36" t="n">
-        <v>1233310706.815902</v>
+        <v>1290039873.482569</v>
       </c>
       <c r="P36" t="n">
         <v>167983086.6666667</v>

--- a/plot/storage/output/ongoing/ongoing_total_q.xlsx
+++ b/plot/storage/output/ongoing/ongoing_total_q.xlsx
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>9406666.666666666</v>
+        <v>830000</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9130000</v>
+        <v>553333.3333333334</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9023333.333333332</v>
+        <v>446666.6666666667</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8140000</v>
+        <v>670000</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>33074212.85</v>
+        <v>26157546.18333333</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>56207746.26666667</v>
+        <v>46067746.26666667</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>78255560.7988304</v>
+        <v>69482783.02105263</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -901,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>95281958.56491227</v>
+        <v>88136958.56491229</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>97240029.12046784</v>
+        <v>90095029.12046784</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>93395790.23157895</v>
+        <v>91500790.23157895</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1051,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>94004738.56491227</v>
+        <v>92109738.56491229</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1095,13 +1095,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>71428571.42857143</v>
+        <v>154761904.7619047</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>173209499.1204678</v>
+        <v>92592276.89824562</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>900432426.8236215</v>
+        <v>900432373.3513993</v>
       </c>
       <c r="P13" t="n">
         <v>31312658.33333333</v>
@@ -1145,13 +1145,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>71428571.42857143</v>
+        <v>154761904.7619047</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>178190924.0210526</v>
+        <v>93212590.6877193</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1513589110.322248</v>
+        <v>1513588949.905581</v>
       </c>
       <c r="P14" t="n">
         <v>31934121.05555555</v>
@@ -1195,13 +1195,13 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>71428571.42857143</v>
+        <v>154761904.7619047</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>181038428.3222222</v>
+        <v>96025294.98888889</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1542359463.77985</v>
+        <v>1542359303.363183</v>
       </c>
       <c r="P15" t="n">
         <v>33940485.27777778</v>
@@ -1245,13 +1245,13 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>83333333.33333333</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>191913950.6</v>
+        <v>106900817.2666667</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1553090081.990973</v>
+        <v>1553089921.574306</v>
       </c>
       <c r="P16" t="n">
         <v>35505104.5</v>
@@ -1295,13 +1295,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>83333333.33333333</v>
       </c>
       <c r="K17" t="n">
         <v>322222.2222222222</v>
       </c>
       <c r="L17" t="n">
-        <v>193579310.8777778</v>
+        <v>108520066.4333333</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1310,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1442749626.21764</v>
+        <v>1442749465.800973</v>
       </c>
       <c r="P17" t="n">
         <v>35542867</v>
@@ -1345,13 +1345,13 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>83333333.33333333</v>
       </c>
       <c r="K18" t="n">
         <v>12517345.66666667</v>
       </c>
       <c r="L18" t="n">
-        <v>306437125.2083333</v>
+        <v>221354825.2083334</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1204648079.750338</v>
+        <v>1204647919.333672</v>
       </c>
       <c r="P18" t="n">
-        <v>37357725.33333334</v>
+        <v>43815195.77777778</v>
       </c>
     </row>
     <row r="19">
@@ -1386,7 +1386,7 @@
         <v>95011829.72222222</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>755555.5555555555</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1395,25 +1395,25 @@
         <v>20000000</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>83333333.33333333</v>
       </c>
       <c r="K19" t="n">
         <v>10800000</v>
       </c>
       <c r="L19" t="n">
-        <v>366111057.2083333</v>
+        <v>279002090.5416667</v>
       </c>
       <c r="M19" t="n">
-        <v>1511111.111111111</v>
+        <v>56311111.1111111</v>
       </c>
       <c r="N19" t="n">
         <v>9166666.666666666</v>
       </c>
       <c r="O19" t="n">
-        <v>1220521095.623354</v>
+        <v>1220520935.206687</v>
       </c>
       <c r="P19" t="n">
-        <v>38163604.5</v>
+        <v>47849810.16666667</v>
       </c>
     </row>
     <row r="20">
@@ -1436,7 +1436,7 @@
         <v>14641077.91666666</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1445,25 +1445,25 @@
         <v>20000000</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>83333333.33333333</v>
       </c>
       <c r="K20" t="n">
         <v>16716666.66666667</v>
       </c>
       <c r="L20" t="n">
-        <v>260726496.6210318</v>
+        <v>172250307.7321429</v>
       </c>
       <c r="M20" t="n">
-        <v>2266666.666666667</v>
+        <v>84466666.66666666</v>
       </c>
       <c r="N20" t="n">
         <v>13750000</v>
       </c>
       <c r="O20" t="n">
-        <v>1288510234.593051</v>
+        <v>1288510074.176384</v>
       </c>
       <c r="P20" t="n">
-        <v>52902692.94444445</v>
+        <v>77470445.02314815</v>
       </c>
     </row>
     <row r="21">
@@ -1486,7 +1486,7 @@
         <v>14641077.91666666</v>
       </c>
       <c r="G21" t="n">
-        <v>61111111.11111111</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1495,25 +1495,25 @@
         <v>28333333.33333333</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>83333333.33333333</v>
       </c>
       <c r="K21" t="n">
         <v>17504166.66666666</v>
       </c>
       <c r="L21" t="n">
-        <v>267875831.6175249</v>
+        <v>177771864.9508582</v>
       </c>
       <c r="M21" t="n">
-        <v>2266666.666666667</v>
+        <v>84466666.66666666</v>
       </c>
       <c r="N21" t="n">
         <v>13750000</v>
       </c>
       <c r="O21" t="n">
-        <v>1477218567.926384</v>
+        <v>1477218407.509718</v>
       </c>
       <c r="P21" t="n">
-        <v>64155672</v>
+        <v>96164197.28472222</v>
       </c>
     </row>
     <row r="22">
@@ -1536,7 +1536,7 @@
         <v>16059158.38888889</v>
       </c>
       <c r="G22" t="n">
-        <v>91666666.66666667</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1545,25 +1545,25 @@
         <v>40555555.55555555</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>83333333.33333333</v>
       </c>
       <c r="K22" t="n">
         <v>17897916.66666666</v>
       </c>
       <c r="L22" t="n">
-        <v>279100366.5522794</v>
+        <v>188996399.8856128</v>
       </c>
       <c r="M22" t="n">
-        <v>2266666.666666667</v>
+        <v>84466666.66666666</v>
       </c>
       <c r="N22" t="n">
         <v>13750000</v>
       </c>
       <c r="O22" t="n">
-        <v>1152808311.516128</v>
+        <v>1152808151.099462</v>
       </c>
       <c r="P22" t="n">
-        <v>74669140.79487179</v>
+        <v>106677666.079594</v>
       </c>
     </row>
     <row r="23">
@@ -1586,7 +1586,7 @@
         <v>426273652.6666666</v>
       </c>
       <c r="G23" t="n">
-        <v>91666666.66666667</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1595,25 +1595,25 @@
         <v>47448634.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>83333333.33333333</v>
       </c>
       <c r="K23" t="n">
         <v>17897916.66666666</v>
       </c>
       <c r="L23" t="n">
-        <v>300136404.8856127</v>
+        <v>212386817.3039134</v>
       </c>
       <c r="M23" t="n">
-        <v>2266666.666666667</v>
+        <v>84466666.66666666</v>
       </c>
       <c r="N23" t="n">
         <v>13750000</v>
       </c>
       <c r="O23" t="n">
-        <v>770399004.5091351</v>
+        <v>770398844.0924685</v>
       </c>
       <c r="P23" t="n">
-        <v>73654417.18376069</v>
+        <v>105662942.4684829</v>
       </c>
     </row>
     <row r="24">
@@ -1636,7 +1636,7 @@
         <v>380900351.3333333</v>
       </c>
       <c r="G24" t="n">
-        <v>91666666.66666667</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1645,25 +1645,25 @@
         <v>47839618.41666666</v>
       </c>
       <c r="J24" t="n">
-        <v>620000000</v>
+        <v>703333333.3333334</v>
       </c>
       <c r="K24" t="n">
         <v>17897916.66666666</v>
       </c>
       <c r="L24" t="n">
-        <v>585599839.4443735</v>
+        <v>381998760.0326087</v>
       </c>
       <c r="M24" t="n">
-        <v>2266666.666666667</v>
+        <v>84466666.66666666</v>
       </c>
       <c r="N24" t="n">
         <v>13750000</v>
       </c>
       <c r="O24" t="n">
-        <v>874723419.8028414</v>
+        <v>874723259.3861747</v>
       </c>
       <c r="P24" t="n">
-        <v>65759204.68376069</v>
+        <v>97767729.9684829</v>
       </c>
     </row>
     <row r="25">
@@ -1686,7 +1686,7 @@
         <v>381178129.1111111</v>
       </c>
       <c r="G25" t="n">
-        <v>91666666.66666667</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1701,19 +1701,19 @@
         <v>17897916.66666666</v>
       </c>
       <c r="L25" t="n">
-        <v>467250540.0890621</v>
+        <v>290032094.0106307</v>
       </c>
       <c r="M25" t="n">
-        <v>2266666.666666667</v>
+        <v>84466666.66666666</v>
       </c>
       <c r="N25" t="n">
         <v>13750000</v>
       </c>
       <c r="O25" t="n">
-        <v>840560706.9972858</v>
+        <v>840560600.0528414</v>
       </c>
       <c r="P25" t="n">
-        <v>1078516611.916084</v>
+        <v>1110525137.200806</v>
       </c>
     </row>
     <row r="26">
@@ -1736,7 +1736,7 @@
         <v>374567018</v>
       </c>
       <c r="G26" t="n">
-        <v>91666666.66666667</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1751,10 +1751,10 @@
         <v>22714692.98245614</v>
       </c>
       <c r="L26" t="n">
-        <v>388960278.1367936</v>
+        <v>395560498.7250289</v>
       </c>
       <c r="M26" t="n">
-        <v>2266666.666666667</v>
+        <v>84466666.66666666</v>
       </c>
       <c r="N26" t="n">
         <v>15949274.38888889</v>
@@ -1763,7 +1763,7 @@
         <v>833579221.5597101</v>
       </c>
       <c r="P26" t="n">
-        <v>84390971.61344211</v>
+        <v>116399496.8981643</v>
       </c>
     </row>
     <row r="27">
@@ -1786,7 +1786,7 @@
         <v>360233684.6666667</v>
       </c>
       <c r="G27" t="n">
-        <v>91666666.66666667</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1801,19 +1801,19 @@
         <v>32348245.61403509</v>
       </c>
       <c r="L27" t="n">
-        <v>285294926.7408036</v>
+        <v>291721147.3290389</v>
       </c>
       <c r="M27" t="n">
-        <v>2266666.666666667</v>
+        <v>84466666.66666666</v>
       </c>
       <c r="N27" t="n">
-        <v>53160022.69444444</v>
+        <v>53160022.69444445</v>
       </c>
       <c r="O27" t="n">
         <v>1025807311.786622</v>
       </c>
       <c r="P27" t="n">
-        <v>171267872.3484848</v>
+        <v>203276397.6332071</v>
       </c>
     </row>
     <row r="28">
@@ -1836,7 +1836,7 @@
         <v>363233684.6666667</v>
       </c>
       <c r="G28" t="n">
-        <v>91666666.66666667</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1851,10 +1851,10 @@
         <v>33775491.7251462</v>
       </c>
       <c r="L28" t="n">
-        <v>2606264869.939217</v>
+        <v>611885534.9718961</v>
       </c>
       <c r="M28" t="n">
-        <v>2266666.666666667</v>
+        <v>84466666.66666666</v>
       </c>
       <c r="N28" t="n">
         <v>71215578.25</v>
@@ -1863,7 +1863,7 @@
         <v>1096717886.894932</v>
       </c>
       <c r="P28" t="n">
-        <v>238145058.6818182</v>
+        <v>270153583.9665404</v>
       </c>
     </row>
     <row r="29">
@@ -1886,7 +1886,7 @@
         <v>360233684.6666667</v>
       </c>
       <c r="G29" t="n">
-        <v>91666666.66666667</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1901,10 +1901,10 @@
         <v>34166892.55847953</v>
       </c>
       <c r="L29" t="n">
-        <v>692929394.2768232</v>
+        <v>696787412.2506794</v>
       </c>
       <c r="M29" t="n">
-        <v>85830927.77777778</v>
+        <v>168030927.7777778</v>
       </c>
       <c r="N29" t="n">
         <v>71215578.25</v>
@@ -1913,7 +1913,7 @@
         <v>1209412331.339376</v>
       </c>
       <c r="P29" t="n">
-        <v>238116811.3333333</v>
+        <v>270125336.6180556</v>
       </c>
     </row>
     <row r="30">
@@ -1936,7 +1936,7 @@
         <v>359205906.8888889</v>
       </c>
       <c r="G30" t="n">
-        <v>92333333.33333334</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>35089114.78070175</v>
       </c>
       <c r="L30" t="n">
-        <v>527063839.2139416</v>
+        <v>450896089.2139416</v>
       </c>
       <c r="M30" t="n">
-        <v>170946391.6666667</v>
+        <v>253146391.6666667</v>
       </c>
       <c r="N30" t="n">
         <v>71215578.25</v>
@@ -1963,7 +1963,7 @@
         <v>1372880585.307631</v>
       </c>
       <c r="P30" t="n">
-        <v>245173820.4444444</v>
+        <v>270724875.2847222</v>
       </c>
     </row>
     <row r="31">
@@ -1983,10 +1983,10 @@
         <v>6944444.444444444</v>
       </c>
       <c r="F31" t="n">
-        <v>358433521.6111111</v>
+        <v>538989077.1666666</v>
       </c>
       <c r="G31" t="n">
-        <v>92333333.33333334</v>
+        <v>377777.7777777778</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>25255781.44736842</v>
       </c>
       <c r="L31" t="n">
-        <v>237832140.8806083</v>
+        <v>241664390.8806083</v>
       </c>
       <c r="M31" t="n">
-        <v>349990836.1111111</v>
+        <v>196835280.5555556</v>
       </c>
       <c r="N31" t="n">
         <v>78715578.25</v>
@@ -2013,7 +2013,7 @@
         <v>1608260702.266695</v>
       </c>
       <c r="P31" t="n">
-        <v>263731188.6666667</v>
+        <v>286053508.2847222</v>
       </c>
     </row>
     <row r="32">
@@ -2033,10 +2033,10 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F32" t="n">
-        <v>8067304273.416666</v>
+        <v>3733970940.083333</v>
       </c>
       <c r="G32" t="n">
-        <v>92333333.33333334</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2051,10 +2051,10 @@
         <v>19339114.78070175</v>
       </c>
       <c r="L32" t="n">
-        <v>265768144.0194972</v>
+        <v>269600394.0194972</v>
       </c>
       <c r="M32" t="n">
-        <v>710346391.6666666</v>
+        <v>171763058.3333333</v>
       </c>
       <c r="N32" t="n">
         <v>75111556.94444445</v>
@@ -2063,7 +2063,7 @@
         <v>1617861042.402749</v>
       </c>
       <c r="P32" t="n">
-        <v>228460800.2222222</v>
+        <v>235901573.4282407</v>
       </c>
     </row>
     <row r="33">
@@ -2083,10 +2083,10 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F33" t="n">
-        <v>3823304273.416667</v>
+        <v>2739970940.083333</v>
       </c>
       <c r="G33" t="n">
-        <v>31222222.22222222</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>400674736.25</v>
@@ -2101,10 +2101,10 @@
         <v>3707535.833333333</v>
       </c>
       <c r="L33" t="n">
-        <v>294609641.3888179</v>
+        <v>298441891.3888179</v>
       </c>
       <c r="M33" t="n">
-        <v>710346391.6666666</v>
+        <v>171763058.3333333</v>
       </c>
       <c r="N33" t="n">
         <v>77070181</v>
@@ -2133,10 +2133,10 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F34" t="n">
-        <v>360633970.7222222</v>
+        <v>902300637.3888888</v>
       </c>
       <c r="G34" t="n">
-        <v>666666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>400674736.25</v>
@@ -2151,10 +2151,10 @@
         <v>3707535.833333333</v>
       </c>
       <c r="L34" t="n">
-        <v>201532680.8995017</v>
+        <v>205364930.8995017</v>
       </c>
       <c r="M34" t="n">
-        <v>710346391.6666666</v>
+        <v>171763058.3333333</v>
       </c>
       <c r="N34" t="n">
         <v>77070181</v>
@@ -2183,10 +2183,10 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F35" t="n">
-        <v>8293365.333333333</v>
+        <v>549960032</v>
       </c>
       <c r="G35" t="n">
-        <v>666666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>400674736.25</v>
@@ -2201,10 +2201,10 @@
         <v>3707535.833333333</v>
       </c>
       <c r="L35" t="n">
-        <v>1878587863.905223</v>
+        <v>272253447.2385566</v>
       </c>
       <c r="M35" t="n">
-        <v>710346391.6666666</v>
+        <v>199540836.1111111</v>
       </c>
       <c r="N35" t="n">
         <v>77070181</v>
@@ -2233,10 +2233,10 @@
         <v>20833333.33333333</v>
       </c>
       <c r="F36" t="n">
-        <v>6666666.666666666</v>
+        <v>548333333.3333334</v>
       </c>
       <c r="G36" t="n">
-        <v>666666.6666666666</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>400674736.25</v>
@@ -2251,10 +2251,10 @@
         <v>3707535.833333333</v>
       </c>
       <c r="L36" t="n">
-        <v>164800269.6666667</v>
+        <v>300484436.3333334</v>
       </c>
       <c r="M36" t="n">
-        <v>710346391.6666666</v>
+        <v>213429725</v>
       </c>
       <c r="N36" t="n">
         <v>77070181</v>
